--- a/PCB/bom.xlsx
+++ b/PCB/bom.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joshf\Documents\Code\USB_IR_Blaster\PCB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83604189-C52B-4B25-8249-01D999DC5704}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C4E610A-FDB7-40D2-92C2-29A7EF793102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{FC31D8FB-3664-43EE-8E32-81502E5E38D7}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="51">
   <si>
     <t>Description</t>
   </si>
@@ -62,9 +62,6 @@
     <t>https://www.waveshare.com/rp2040-tiny.htm?srsltid=AfmBOorKS5aQ4y4EkMcvGGjNeNLi7KiRloSdQONyjE8Fxqy6lYQzbGGq</t>
   </si>
   <si>
-    <t>Waveshare RP2040-Tiny</t>
-  </si>
-  <si>
     <t>Libraries</t>
   </si>
   <si>
@@ -177,6 +174,24 @@
   </si>
   <si>
     <t>https://www.digikey.com/en/models/1760676?tab=ultralibrarian</t>
+  </si>
+  <si>
+    <t>Waveshare</t>
+  </si>
+  <si>
+    <t>27.4 Ohms ±1% 0.25W, 1/4W Chip Resistor 1206 (3216 Metric) Automotive AEC-Q200 Thick Film</t>
+  </si>
+  <si>
+    <t>RMCF1206FT27R4CT-ND</t>
+  </si>
+  <si>
+    <t>RMCF1206FT27R4</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/stackpole-electronics-inc/RMCF1206FT27R4/1759794</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/models/1759794?tab=ultralibrarian</t>
   </si>
 </sst>
 </file>
@@ -571,7 +586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CDCC247-279C-4A9F-A582-D4D49D3E2219}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="15.265625" customWidth="1"/>
@@ -601,18 +616,18 @@
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="128.25" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -623,140 +638,166 @@
         <v>1</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="142.5" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="F3" s="2">
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="142.5" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="F4" s="2">
         <v>12</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F5" s="2">
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="114" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F6" s="2">
         <v>3</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="114" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="F7" s="2">
         <v>1</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="114" x14ac:dyDescent="0.45">
+      <c r="A8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" s="2">
+        <v>2</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
